--- a/data/trans_orig/IP28_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP28_R-Provincia-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52895</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59507</t>
+          <t>59509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103936</t>
+          <t>103340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109644</t>
+          <t>109657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94308</t>
+          <t>94555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100272</t>
+          <t>100273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104817</t>
+          <t>105464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>202211</t>
+          <t>202116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208348</t>
+          <t>208352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65932</t>
+          <t>65906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133438</t>
+          <t>132802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69793</t>
+          <t>69782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74208</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146624</t>
+          <t>146586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150882</t>
+          <t>150872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38649</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41500</t>
+          <t>41334</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82516</t>
+          <t>82099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52081</t>
+          <t>52740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111194</t>
+          <t>110929</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123223</t>
+          <t>122802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128588</t>
+          <t>128589</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>253174</t>
+          <t>254297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>147521</t>
+          <t>147272</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>153494</t>
+          <t>153397</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>157413</t>
+          <t>157410</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>307254</t>
+          <t>307007</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>314771</t>
+          <t>314710</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>655049</t>
+          <t>655994</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>665664</t>
+          <t>665588</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>700814</t>
+          <t>700823</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>710926</t>
+          <t>710732</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1360837</t>
+          <t>1360707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1374632</t>
+          <t>1374213</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48279</t>
+          <t>47742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55016</t>
+          <t>55097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105224</t>
+          <t>105446</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111369</t>
+          <t>111357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91496</t>
+          <t>90948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95329</t>
+          <t>95249</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189418</t>
+          <t>188749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>195375</t>
+          <t>195403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54827</t>
+          <t>55275</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60073</t>
+          <t>59320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117198</t>
+          <t>117079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122184</t>
+          <t>122187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,44 +5105,44 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4615</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>6,25%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6094</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>66361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,49 +5213,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>92,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>72817</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>69203</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>73818</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>93,75%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>72817</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>67724</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>73818</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>204</t>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138831</t>
+          <t>139087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144998</t>
+          <t>144989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33958</t>
+          <t>33840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>39064</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74959</t>
+          <t>75720</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80057</t>
+          <t>80061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48309</t>
+          <t>47693</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53504</t>
+          <t>53497</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51239</t>
+          <t>51043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102366</t>
+          <t>102854</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108958</t>
+          <t>108967</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119506</t>
+          <t>119253</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125180</t>
+          <t>125754</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>247159</t>
+          <t>247092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>251683</t>
+          <t>251685</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142876</t>
+          <t>143551</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>149502</t>
+          <t>149553</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>157605</t>
+          <t>157969</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163547</t>
+          <t>163651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>304375</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>312300</t>
+          <t>312212</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>626303</t>
+          <t>626836</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>638830</t>
+          <t>638084</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>671509</t>
+          <t>671264</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>682523</t>
+          <t>682334</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1302059</t>
+          <t>1302003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1317979</t>
+          <t>1318615</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43681</t>
+          <t>44355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48667</t>
+          <t>48186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94909</t>
+          <t>94368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99445</t>
+          <t>99448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90755</t>
+          <t>91592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97043</t>
+          <t>97535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>190739</t>
+          <t>190206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>195576</t>
+          <t>195570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66751</t>
+          <t>67678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66956</t>
+          <t>67126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137846</t>
+          <t>137922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38865</t>
+          <t>39291</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83278</t>
+          <t>82980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48432</t>
+          <t>47807</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96769</t>
+          <t>96147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119551</t>
+          <t>119948</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124916</t>
+          <t>124922</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124333</t>
+          <t>124329</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>129310</t>
+          <t>129979</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>245544</t>
+          <t>245722</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>253456</t>
+          <t>253447</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>525</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137000</t>
+          <t>136996</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147783</t>
+          <t>147797</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>286565</t>
+          <t>285814</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>290889</t>
+          <t>290877</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>621744</t>
+          <t>622033</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>630026</t>
+          <t>630001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>655961</t>
+          <t>655726</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>664147</t>
+          <t>664136</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1280921</t>
+          <t>1280509</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1292547</t>
+          <t>1292470</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68479</t>
+          <t>68798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74241</t>
+          <t>74086</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78884</t>
+          <t>78878</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146291</t>
+          <t>145778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151638</t>
+          <t>151561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121229</t>
+          <t>119843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122010</t>
+          <t>122643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>247048</t>
+          <t>246241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54856</t>
+          <t>54930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122112</t>
+          <t>121794</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>61506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69140</t>
+          <t>69183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138708</t>
+          <t>139026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147378</t>
+          <t>147328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35884</t>
+          <t>36453</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71479</t>
+          <t>71019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52162</t>
+          <t>52222</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98677</t>
+          <t>98357</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116596</t>
+          <t>115790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123832</t>
+          <t>123630</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149571</t>
+          <t>149543</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269525</t>
+          <t>269529</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>277973</t>
+          <t>278305</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>148692</t>
+          <t>149467</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280527</t>
+          <t>280272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>16868</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>645521</t>
+          <t>645772</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>657450</t>
+          <t>657626</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>744770</t>
+          <t>745024</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>754838</t>
+          <t>754818</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1395948</t>
+          <t>1395189</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1410273</t>
+          <t>1410718</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
